--- a/outputs_xlsx_solution/test_new3.4-wide-NC-1.xlsx
+++ b/outputs_xlsx_solution/test_new3.4-wide-NC-1.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>fadd F4, F1, F1</t>
   </si>
   <si>
@@ -156,6 +159,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -705,7 +711,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3">
@@ -725,13 +731,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -751,13 +757,16 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
       </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -777,13 +786,19 @@
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>15</v>
       </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -806,10 +821,10 @@
         <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -829,7 +844,7 @@
         <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H7" t="s">
         <v>14</v>
@@ -841,10 +856,10 @@
         <v>14</v>
       </c>
       <c r="K7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -864,7 +879,10 @@
         <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
+        <v>15</v>
       </c>
       <c r="I8" t="s">
         <v>14</v>
@@ -876,10 +894,10 @@
         <v>14</v>
       </c>
       <c r="L8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -899,7 +917,7 @@
         <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L9" t="s">
         <v>14</v>
@@ -914,7 +932,7 @@
         <v>14</v>
       </c>
       <c r="P9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -925,17 +943,20 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" t="s">
+        <v>9</v>
+      </c>
+      <c r="H10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" t="s">
         <v>15</v>
       </c>
-      <c r="F10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" t="s">
-        <v>9</v>
-      </c>
-      <c r="H10" t="s">
-        <v>20</v>
-      </c>
       <c r="J10" t="s">
         <v>14</v>
       </c>
@@ -946,10 +967,10 @@
         <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Q10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -960,7 +981,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -969,16 +990,16 @@
         <v>9</v>
       </c>
       <c r="H11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M11" t="s">
         <v>14</v>
@@ -990,10 +1011,10 @@
         <v>14</v>
       </c>
       <c r="P11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="R11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -1013,7 +1034,7 @@
         <v>9</v>
       </c>
       <c r="K12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P12" t="s">
         <v>14</v>
@@ -1028,7 +1049,7 @@
         <v>14</v>
       </c>
       <c r="T12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -1039,7 +1060,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -1048,16 +1069,16 @@
         <v>9</v>
       </c>
       <c r="K13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P13" t="s">
         <v>14</v>
       </c>
       <c r="Q13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="U13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -1068,7 +1089,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -1080,10 +1101,10 @@
         <v>14</v>
       </c>
       <c r="L14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="V14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -1094,7 +1115,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -1106,10 +1127,10 @@
         <v>14</v>
       </c>
       <c r="M15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -1120,7 +1141,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G16" t="s">
         <v>5</v>
@@ -1129,16 +1150,16 @@
         <v>9</v>
       </c>
       <c r="L16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M16" t="s">
         <v>14</v>
       </c>
       <c r="N16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="X16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -1149,7 +1170,7 @@
         <v>60</v>
       </c>
       <c r="C17" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" t="s">
         <v>5</v>
@@ -1158,16 +1179,16 @@
         <v>9</v>
       </c>
       <c r="L17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N17" t="s">
         <v>14</v>
       </c>
       <c r="O17" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -1178,7 +1199,7 @@
         <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="O18" t="s">
         <v>5</v>
@@ -1187,7 +1208,7 @@
         <v>9</v>
       </c>
       <c r="Q18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R18" t="s">
         <v>14</v>
@@ -1199,10 +1220,10 @@
         <v>14</v>
       </c>
       <c r="U18" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Z18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
@@ -1222,7 +1243,7 @@
         <v>9</v>
       </c>
       <c r="Q19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T19" t="s">
         <v>14</v>
@@ -1237,10 +1258,10 @@
         <v>14</v>
       </c>
       <c r="X19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1251,7 +1272,7 @@
         <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O20" t="s">
         <v>5</v>
@@ -1260,16 +1281,16 @@
         <v>9</v>
       </c>
       <c r="Q20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U20" t="s">
         <v>14</v>
       </c>
       <c r="V20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AB20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -1280,7 +1301,7 @@
         <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O21" t="s">
         <v>5</v>
@@ -1289,16 +1310,16 @@
         <v>9</v>
       </c>
       <c r="Q21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="R21" t="s">
         <v>14</v>
       </c>
       <c r="S21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AC21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1309,7 +1330,7 @@
         <v>52</v>
       </c>
       <c r="C22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P22" t="s">
         <v>5</v>
@@ -1318,16 +1339,16 @@
         <v>9</v>
       </c>
       <c r="R22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S22" t="s">
         <v>14</v>
       </c>
       <c r="T22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AD22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1338,7 +1359,7 @@
         <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="P23" t="s">
         <v>5</v>
@@ -1347,16 +1368,16 @@
         <v>9</v>
       </c>
       <c r="R23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T23" t="s">
         <v>14</v>
       </c>
       <c r="U23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AE23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24">
@@ -1367,7 +1388,7 @@
         <v>60</v>
       </c>
       <c r="C24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P24" t="s">
         <v>5</v>
@@ -1376,16 +1397,16 @@
         <v>9</v>
       </c>
       <c r="R24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U24" t="s">
         <v>14</v>
       </c>
       <c r="V24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25">
@@ -1396,7 +1417,7 @@
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Q25" t="s">
         <v>5</v>
@@ -1405,7 +1426,7 @@
         <v>9</v>
       </c>
       <c r="S25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U25" t="s">
         <v>14</v>
@@ -1417,10 +1438,10 @@
         <v>14</v>
       </c>
       <c r="X25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AG25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26">
@@ -1440,10 +1461,10 @@
         <v>9</v>
       </c>
       <c r="S26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X26" t="s">
         <v>14</v>
@@ -1458,10 +1479,10 @@
         <v>14</v>
       </c>
       <c r="AB26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1472,7 +1493,7 @@
         <v>44</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="Q27" t="s">
         <v>5</v>
@@ -1481,16 +1502,16 @@
         <v>9</v>
       </c>
       <c r="T27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X27" t="s">
         <v>14</v>
       </c>
       <c r="Y27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -1501,7 +1522,7 @@
         <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Q28" t="s">
         <v>5</v>
@@ -1510,16 +1531,16 @@
         <v>9</v>
       </c>
       <c r="T28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="U28" t="s">
         <v>14</v>
       </c>
       <c r="V28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AJ28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1530,7 +1551,7 @@
         <v>52</v>
       </c>
       <c r="C29" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R29" t="s">
         <v>5</v>
@@ -1539,19 +1560,19 @@
         <v>9</v>
       </c>
       <c r="T29" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="U29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="V29" t="s">
         <v>14</v>
       </c>
       <c r="W29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AK29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="30">
@@ -1562,7 +1583,7 @@
         <v>56</v>
       </c>
       <c r="C30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R30" t="s">
         <v>5</v>
@@ -1571,19 +1592,19 @@
         <v>9</v>
       </c>
       <c r="U30" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="V30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W30" t="s">
         <v>14</v>
       </c>
       <c r="X30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AL30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -1594,7 +1615,7 @@
         <v>60</v>
       </c>
       <c r="C31" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R31" t="s">
         <v>5</v>
@@ -1603,19 +1624,19 @@
         <v>9</v>
       </c>
       <c r="V31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="W31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="X31" t="s">
         <v>14</v>
       </c>
       <c r="Y31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AM31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -1626,7 +1647,7 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="S32" t="s">
         <v>5</v>
@@ -1635,10 +1656,10 @@
         <v>9</v>
       </c>
       <c r="W32" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="X32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y32" t="s">
         <v>14</v>
@@ -1650,10 +1671,10 @@
         <v>14</v>
       </c>
       <c r="AB32" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -1673,10 +1694,10 @@
         <v>9</v>
       </c>
       <c r="X33" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Y33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB33" t="s">
         <v>14</v>
@@ -1691,10 +1712,10 @@
         <v>14</v>
       </c>
       <c r="AF33" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -1705,7 +1726,7 @@
         <v>44</v>
       </c>
       <c r="C34" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="S34" t="s">
         <v>5</v>
@@ -1714,19 +1735,19 @@
         <v>9</v>
       </c>
       <c r="Y34" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="Z34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB34" t="s">
         <v>14</v>
       </c>
       <c r="AC34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AP34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -1737,7 +1758,7 @@
         <v>48</v>
       </c>
       <c r="C35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="S35" t="s">
         <v>5</v>
@@ -1746,19 +1767,19 @@
         <v>9</v>
       </c>
       <c r="Z35" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AA35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB35" t="s">
         <v>14</v>
       </c>
       <c r="AC35" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
@@ -1769,7 +1790,7 @@
         <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="T36" t="s">
         <v>5</v>
@@ -1778,19 +1799,19 @@
         <v>9</v>
       </c>
       <c r="AA36" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AB36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC36" t="s">
         <v>14</v>
       </c>
       <c r="AD36" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
@@ -1801,7 +1822,7 @@
         <v>56</v>
       </c>
       <c r="C37" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="T37" t="s">
         <v>5</v>
@@ -1810,19 +1831,19 @@
         <v>9</v>
       </c>
       <c r="AB37" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AC37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD37" t="s">
         <v>14</v>
       </c>
       <c r="AE37" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38">
@@ -1833,7 +1854,7 @@
         <v>60</v>
       </c>
       <c r="C38" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T38" t="s">
         <v>5</v>
@@ -1842,19 +1863,19 @@
         <v>9</v>
       </c>
       <c r="AC38" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AD38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE38" t="s">
         <v>14</v>
       </c>
       <c r="AF38" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
@@ -1865,7 +1886,7 @@
         <v>36</v>
       </c>
       <c r="C39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U39" t="s">
         <v>5</v>
@@ -1874,10 +1895,10 @@
         <v>9</v>
       </c>
       <c r="AD39" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF39" t="s">
         <v>14</v>
@@ -1889,10 +1910,10 @@
         <v>14</v>
       </c>
       <c r="AI39" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -1912,10 +1933,10 @@
         <v>9</v>
       </c>
       <c r="AE40" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AF40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG40" t="s">
         <v>14</v>
@@ -1930,10 +1951,10 @@
         <v>14</v>
       </c>
       <c r="AK40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="41">
@@ -1944,7 +1965,7 @@
         <v>44</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="U41" t="s">
         <v>5</v>
@@ -1953,19 +1974,19 @@
         <v>9</v>
       </c>
       <c r="AF41" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI41" t="s">
         <v>14</v>
       </c>
       <c r="AJ41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -1976,7 +1997,7 @@
         <v>48</v>
       </c>
       <c r="C42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="U42" t="s">
         <v>5</v>
@@ -1985,19 +2006,19 @@
         <v>9</v>
       </c>
       <c r="AG42" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AH42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI42" t="s">
         <v>14</v>
       </c>
       <c r="AJ42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -2008,7 +2029,7 @@
         <v>52</v>
       </c>
       <c r="C43" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="V43" t="s">
         <v>5</v>
@@ -2017,19 +2038,19 @@
         <v>9</v>
       </c>
       <c r="AH43" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ43" t="s">
         <v>14</v>
       </c>
       <c r="AK43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AY43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
@@ -2040,7 +2061,7 @@
         <v>56</v>
       </c>
       <c r="C44" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="V44" t="s">
         <v>5</v>
@@ -2049,19 +2070,19 @@
         <v>9</v>
       </c>
       <c r="AI44" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK44" t="s">
         <v>14</v>
       </c>
       <c r="AL44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AZ44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
@@ -2072,7 +2093,7 @@
         <v>60</v>
       </c>
       <c r="C45" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="V45" t="s">
         <v>5</v>
@@ -2081,19 +2102,19 @@
         <v>9</v>
       </c>
       <c r="AJ45" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL45" t="s">
         <v>14</v>
       </c>
       <c r="AM45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -2104,7 +2125,7 @@
         <v>64</v>
       </c>
       <c r="C46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AM46" t="s">
         <v>5</v>
@@ -2113,7 +2134,7 @@
         <v>9</v>
       </c>
       <c r="AO46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP46" t="s">
         <v>14</v>
@@ -2125,10 +2146,10 @@
         <v>14</v>
       </c>
       <c r="AS46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
@@ -2148,7 +2169,7 @@
         <v>9</v>
       </c>
       <c r="AO47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP47" t="s">
         <v>14</v>
@@ -2163,10 +2184,10 @@
         <v>14</v>
       </c>
       <c r="AT47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
@@ -2177,7 +2198,7 @@
         <v>72</v>
       </c>
       <c r="C48" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM48" t="s">
         <v>5</v>
@@ -2186,16 +2207,16 @@
         <v>9</v>
       </c>
       <c r="AO48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS48" t="s">
         <v>14</v>
       </c>
       <c r="AT48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
@@ -2206,7 +2227,7 @@
         <v>76</v>
       </c>
       <c r="C49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM49" t="s">
         <v>5</v>
@@ -2215,21 +2236,21 @@
         <v>9</v>
       </c>
       <c r="AO49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT49" t="s">
         <v>14</v>
       </c>
       <c r="AU49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BE49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52">
@@ -2237,7 +2258,7 @@
         <v>5</v>
       </c>
       <c r="B52" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
@@ -2245,15 +2266,15 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="55">
@@ -2261,39 +2282,55 @@
         <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B56" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B57" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B58" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
+        <v>27</v>
+      </c>
+      <c r="B59" t="s">
         <v>39</v>
       </c>
-      <c r="B59" t="s">
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
         <v>40</v>
+      </c>
+      <c r="B60" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
